--- a/fogli/sondaggio-per-iniziare-compressibilita.xlsx
+++ b/fogli/sondaggio-per-iniziare-compressibilita.xlsx
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Tensioni efficaci</t>
+          <t>Terreni saturi</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
